--- a/projectss.xlsx
+++ b/projectss.xlsx
@@ -662,8 +662,8 @@
       <c r="F2" t="str">
         <v>آقای بهزادی</v>
       </c>
-      <c r="G2">
-        <v>18</v>
+      <c r="G2" t="str">
+        <v>20</v>
       </c>
       <c r="H2">
         <v>850</v>

--- a/projectss.xlsx
+++ b/projectss.xlsx
@@ -663,7 +663,7 @@
         <v>آقای بهزادی</v>
       </c>
       <c r="G2" t="str">
-        <v>20</v>
+        <v>332</v>
       </c>
       <c r="H2">
         <v>850</v>

--- a/projectss.xlsx
+++ b/projectss.xlsx
@@ -663,7 +663,7 @@
         <v>آقای بهزادی</v>
       </c>
       <c r="G2" t="str">
-        <v>332</v>
+        <v>18</v>
       </c>
       <c r="H2">
         <v>850</v>

--- a/projectss.xlsx
+++ b/projectss.xlsx
@@ -663,7 +663,7 @@
         <v>آقای بهزادی</v>
       </c>
       <c r="G2" t="str">
-        <v>18</v>
+        <v>323</v>
       </c>
       <c r="H2">
         <v>850</v>

--- a/projectss.xlsx
+++ b/projectss.xlsx
@@ -663,7 +663,7 @@
         <v>آقای بهزادی</v>
       </c>
       <c r="G2" t="str">
-        <v>323</v>
+        <v>18</v>
       </c>
       <c r="H2">
         <v>850</v>
